--- a/302/food/2026-02-03-sm.xlsx
+++ b/302/food/2026-02-03-sm.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Лист_1" sheetId="1" state="visible" r:id="rId1"/>
@@ -46,7 +46,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -82,19 +82,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -305,7 +292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -313,17 +300,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -335,79 +325,70 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -488,9 +469,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -528,9 +509,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -565,7 +546,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -600,7 +581,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -799,19 +780,19 @@
           <t>Школа</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="32" t="inlineStr">
         <is>
           <t>МБОУ « Гимназия №9 с.Сержень-юрт»</t>
         </is>
       </c>
-      <c r="C1" s="35" t="n"/>
-      <c r="D1" s="36" t="n"/>
+      <c r="C1" s="33" t="n"/>
+      <c r="D1" s="34" t="n"/>
       <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Отд./корп</t>
         </is>
       </c>
-      <c r="F1" s="3" t="n"/>
+      <c r="F1" s="32" t="n"/>
       <c r="G1" s="4" t="n"/>
       <c r="I1" s="2" t="inlineStr">
         <is>
@@ -887,17 +868,17 @@
           <t>Завтрак</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>гор.блюдо</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>Сырники из творога запеченые</t>
         </is>
@@ -957,7 +938,7 @@
         <v>36.71</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>81.8</v>
+        <v>83.8</v>
       </c>
       <c r="H6" s="24" t="n">
         <v>1.5</v>
@@ -1071,13 +1052,13 @@
           <t>Обед</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>закуска</t>
         </is>
       </c>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="12" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="13" t="n"/>
       <c r="E11" s="26" t="n"/>
       <c r="F11" s="26" t="n"/>
       <c r="G11" s="26" t="n"/>
